--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DC7FC2-C234-4561-98B5-B71B93D6A76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B230ACE70A49270D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A12895-E173-4168-83E1-69EFC0A509CD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 09-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 14-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B230ACE70A49270D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A12895-E173-4168-83E1-69EFC0A509CD}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B234D56F69F1870D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AFDCFCA-1E10-44FA-8F05-5CE623F8330F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B234D56F69F1870D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AFDCFCA-1E10-44FA-8F05-5CE623F8330F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1982F9-AFCA-4D38-A105-43CF49E76CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1982F9-AFCA-4D38-A105-43CF49E76CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C5E84A-4852-40B9-8514-CA3BE5AE28C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 14-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 17-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C5E84A-4852-40B9-8514-CA3BE5AE28C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA2C1D6-4B8F-4922-B6DD-95E89616A284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA2C1D6-4B8F-4922-B6DD-95E89616A284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B2349DEB792B070D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB2727D0-2DE3-4984-9665-0C5EA4116460}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 17-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 18-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B2349DEB792B070D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB2727D0-2DE3-4984-9665-0C5EA4116460}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B2383DEF089B071D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A224E131-C50A-4E35-940B-AF571C432AC3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 18-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 21-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B2383DEF089B071D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A224E131-C50A-4E35-940B-AF571C432AC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114807A5-1F4F-47B8-B230-00A7D0B5C28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114807A5-1F4F-47B8-B230-00A7D0B5C28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B41B7A-CB6E-4B91-96AF-63629BA1893A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 21-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 22-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B41B7A-CB6E-4B91-96AF-63629BA1893A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8221EC-14CE-40F1-BC31-1F826B5D7825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8221EC-14CE-40F1-BC31-1F826B5D7825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EEA606-004F-4584-ABF8-EF6776381702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 22-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 23-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EEA606-004F-4584-ABF8-EF6776381702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B230026749ADC71D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16497B17-0C8B-4362-AAF3-81FCE93CC339}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98CB53996772B230026749ADC71D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16497B17-0C8B-4362-AAF3-81FCE93CC339}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C12579A69F2B23277EF0A22871D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0391E26-E83E-4AFD-AE43-79E0B431971B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 23-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 24-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -61,7 +61,7 @@
     <t>Xdont (CGM)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C12579A69F2B23277EF0A22871D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0391E26-E83E-4AFD-AE43-79E0B431971B}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C12579A69F2B236B1EF1B9E670D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90A8B459-45B7-49D2-BA63-437679D9ABBE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C12579A69F2B236B1EF1B9E670D896AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90A8B459-45B7-49D2-BA63-437679D9ABBE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471F7EC6-4A76-45EF-A3AD-84255290ADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 24-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 28-09-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -539,9 +539,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -721,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -776,7 +776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -874,7 +874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>56</v>
       </c>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8221EC-14CE-40F1-BC31-1F826B5D7825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{220E1D99-98B6-4D09-B922-F6CFA745090C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 22-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 07-10-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -61,7 +61,7 @@
     <t>Xdont (CGM)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471F7EC6-4A76-45EF-A3AD-84255290ADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9DFE8C-1B54-40B3-9D51-D32D0A1A3684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 28-09-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 07-10-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9DFE8C-1B54-40B3-9D51-D32D0A1A3684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C12579A69F2B2321F6B6932C71D896A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07D1C33B-6A15-43D9-AE7E-84AE7247F468}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 07-10-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 08-10-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C12579A69F2B2321F6B6932C71D896A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07D1C33B-6A15-43D9-AE7E-84AE7247F468}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7ABBC4-0A15-4FD3-880F-E275514B54B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 08-10-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 09-10-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7ABBC4-0A15-4FD3-880F-E275514B54B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985BE093-EF39-44DE-848F-0C9EC558E7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fysioterapisystemer_excel.XLSX
+++ b/html/Fysioterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985BE093-EF39-44DE-848F-0C9EC558E7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C12579A69F2B230546F3BED671D896A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA3E4562-DC21-472C-B0C5-536820E316F6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fysioterapisystemer">'Opdateret d. 09-10-2026'!$A$1:$L$30</definedName>
+    <definedName name="Fysioterapisystemer">'Opdateret d. 23-10-2026'!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
